--- a/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
+++ b/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
@@ -1599,7 +1599,7 @@
       <c r="P10" s="45" t="n"/>
       <c r="Q10" s="1" t="n"/>
     </row>
-    <row r="11" ht="75" customFormat="1" customHeight="1" s="98">
+    <row r="11" ht="88" customFormat="1" customHeight="1" s="98">
       <c r="A11" s="15" t="n">
         <v>6</v>
       </c>
@@ -1644,12 +1644,11 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
-            <t>・10/9 第2回定例　SCより10/8に今回解体範囲のアスベスト検体採取を実施したと報告。速報は来週中の見込み、含有の場合はすぐに見積を提出する</t>
+            <t>・10/9 第2回定例　SCより10/8に今回解体範囲のアスベスト検体採取を実施したと報告。速報は来週中の見込み、含有の場合はすぐに見積を提出する
+・10/16　SCより見積を提出済み</t>
           </r>
         </is>
       </c>

--- a/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
+++ b/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
@@ -1600,34 +1600,34 @@
       <c r="Q10" s="1" t="n"/>
     </row>
     <row r="11" ht="88" customFormat="1" customHeight="1" s="98">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="149" t="n">
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="133" t="n">
         <v>46283</v>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="37" t="inlineStr">
         <is>
           <t>アスベスト含有建材事前調査を10月初旬に実施予定</t>
         </is>
       </c>
-      <c r="K11" s="89" t="inlineStr">
+      <c r="K11" s="40" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L11" s="33" t="inlineStr">
+      <c r="L11" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1652,12 +1652,14 @@
           </r>
         </is>
       </c>
-      <c r="M11" s="150" t="n"/>
-      <c r="N11" s="151" t="n">
+      <c r="M11" s="148" t="n"/>
+      <c r="N11" s="135" t="n">
         <v>46311</v>
       </c>
-      <c r="O11" s="152" t="n"/>
-      <c r="P11" s="20" t="n"/>
+      <c r="O11" s="136" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P11" s="45" t="n"/>
       <c r="Q11" s="1" t="n"/>
     </row>
     <row r="12" ht="53.1" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
+++ b/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
@@ -3551,59 +3551,155 @@
       <c r="O43" s="155" t="n"/>
       <c r="P43" s="43" t="n"/>
     </row>
-    <row r="44" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A44" s="15" t="n"/>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="149" t="n"/>
-      <c r="I44" s="24" t="n"/>
-      <c r="J44" s="18" t="n"/>
-      <c r="K44" s="17" t="n"/>
-      <c r="L44" s="25" t="n"/>
-      <c r="M44" s="153" t="n"/>
-      <c r="N44" s="149" t="n"/>
-      <c r="O44" s="19" t="n"/>
-      <c r="P44" s="20" t="n"/>
-    </row>
-    <row r="45" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A45" s="15" t="n"/>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="149" t="n"/>
-      <c r="I45" s="24" t="n"/>
-      <c r="J45" s="18" t="n"/>
-      <c r="K45" s="17" t="n"/>
-      <c r="L45" s="25" t="n"/>
-      <c r="M45" s="153" t="n"/>
-      <c r="N45" s="149" t="n"/>
-      <c r="O45" s="19" t="n"/>
-      <c r="P45" s="20" t="n"/>
-    </row>
-    <row r="46" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A46" s="15" t="n"/>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="149" t="n"/>
-      <c r="I46" s="24" t="n"/>
-      <c r="J46" s="18" t="n"/>
-      <c r="K46" s="17" t="n"/>
-      <c r="L46" s="25" t="n"/>
-      <c r="M46" s="153" t="n"/>
-      <c r="N46" s="149" t="n"/>
-      <c r="O46" s="19" t="n"/>
-      <c r="P46" s="20" t="n"/>
+    <row r="44" ht="49" customFormat="1" customHeight="1" s="98">
+      <c r="A44" s="46" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C44" s="47" t="n"/>
+      <c r="D44" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="n"/>
+      <c r="F44" s="47" t="n"/>
+      <c r="G44" s="47" t="n"/>
+      <c r="H44" s="151" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I44" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J44" s="49" t="inlineStr">
+        <is>
+          <t>吸音ルーバー（受領図）の確認事項
+・設備・電気の点検口</t>
+        </is>
+      </c>
+      <c r="K44" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L44" s="50" t="inlineStr">
+        <is>
+          <t>・10/23 第6回分科会　ルーバー部の点検口は4か所（位置は要確認）
+・プルボックス上は取外し式ルーバー1本で点検対応する方向
+・天井との取合いはクリアランス20mmで確認（要確認）</t>
+        </is>
+      </c>
+      <c r="M44" s="154" t="n"/>
+      <c r="N44" s="151" t="n"/>
+      <c r="O44" s="155" t="n"/>
+      <c r="P44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="49" customFormat="1" customHeight="1" s="98">
+      <c r="A45" s="46" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C45" s="47" t="n"/>
+      <c r="D45" s="47" t="n"/>
+      <c r="E45" s="47" t="n"/>
+      <c r="F45" s="47" t="n"/>
+      <c r="G45" s="47" t="n"/>
+      <c r="H45" s="151" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I45" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J45" s="49" t="inlineStr">
+        <is>
+          <t>アルミルーバー（受領図）の確認事項</t>
+        </is>
+      </c>
+      <c r="K45" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L45" s="50" t="inlineStr">
+        <is>
+          <t>・10/23 第6回分科会　下部の1本は上と面を合わせる／ジョイントを設ける（要確認）
+・調整は20mm程度可能。当たる場合は手前を上と合わせる（要確認）</t>
+        </is>
+      </c>
+      <c r="M45" s="154" t="n"/>
+      <c r="N45" s="151" t="n"/>
+      <c r="O45" s="155" t="n"/>
+      <c r="P45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="75" customFormat="1" customHeight="1" s="98">
+      <c r="A46" s="46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C46" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E46" s="47" t="n"/>
+      <c r="F46" s="47" t="n"/>
+      <c r="G46" s="47" t="n"/>
+      <c r="H46" s="151" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I46" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J46" s="49" t="inlineStr">
+        <is>
+          <t>建具（受領図・打合図）の確認事項
+・AD（受）
+・ハンガードア（受）
+・SD点検口（打）</t>
+        </is>
+      </c>
+      <c r="K46" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L46" s="50" t="inlineStr">
+        <is>
+          <t>・10/23 第6回分科会　AD：エンジンの配線がランマ上から見える→ランマ中央に新設して隠す（要確認）
+・ハンガードア：床レールは飛び出さないタイプで作図。上部吊金具の耐荷重に懸念あり（要確認）
+・SD点検口は塗装とする</t>
+        </is>
+      </c>
+      <c r="M46" s="154" t="n"/>
+      <c r="N46" s="151" t="n"/>
+      <c r="O46" s="155" t="n"/>
+      <c r="P46" s="43" t="n"/>
     </row>
     <row r="47" ht="40.05" customFormat="1" customHeight="1" s="98">
       <c r="A47" s="15" t="n"/>

--- a/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
+++ b/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
@@ -3597,7 +3597,9 @@
         </is>
       </c>
       <c r="M44" s="154" t="n"/>
-      <c r="N44" s="151" t="n"/>
+      <c r="N44" s="151" t="n">
+        <v>46325</v>
+      </c>
       <c r="O44" s="155" t="n"/>
       <c r="P44" s="43" t="n"/>
     </row>
@@ -3641,7 +3643,9 @@
         </is>
       </c>
       <c r="M45" s="154" t="n"/>
-      <c r="N45" s="151" t="n"/>
+      <c r="N45" s="151" t="n">
+        <v>46325</v>
+      </c>
       <c r="O45" s="155" t="n"/>
       <c r="P45" s="43" t="n"/>
     </row>
@@ -3697,7 +3701,9 @@
         </is>
       </c>
       <c r="M46" s="154" t="n"/>
-      <c r="N46" s="151" t="n"/>
+      <c r="N46" s="151" t="n">
+        <v>46325</v>
+      </c>
       <c r="O46" s="155" t="n"/>
       <c r="P46" s="43" t="n"/>
     </row>

--- a/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
+++ b/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
@@ -3403,7 +3403,9 @@
         </is>
       </c>
       <c r="M40" s="157" t="n"/>
-      <c r="N40" s="156" t="n"/>
+      <c r="N40" s="156" t="n">
+        <v>46325</v>
+      </c>
       <c r="O40" s="146" t="n"/>
       <c r="P40" s="123" t="n"/>
       <c r="Q40" s="1" t="n"/>
@@ -3496,7 +3498,9 @@
         </is>
       </c>
       <c r="M42" s="154" t="n"/>
-      <c r="N42" s="151" t="n"/>
+      <c r="N42" s="151" t="n">
+        <v>46325</v>
+      </c>
       <c r="O42" s="155" t="n"/>
       <c r="P42" s="43" t="n"/>
       <c r="Q42" s="1" t="n"/>
@@ -3547,7 +3551,9 @@
         </is>
       </c>
       <c r="M43" s="154" t="n"/>
-      <c r="N43" s="151" t="n"/>
+      <c r="N43" s="151" t="n">
+        <v>46325</v>
+      </c>
       <c r="O43" s="155" t="n"/>
       <c r="P43" s="43" t="n"/>
     </row>

--- a/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
+++ b/椙山改修/261030_課題リスト（1021_理事長プレゼン後）.xlsx
@@ -2701,7 +2701,7 @@
       </c>
       <c r="M27" s="153" t="n"/>
       <c r="N27" s="151" t="n">
-        <v>46316</v>
+        <v>46325</v>
       </c>
       <c r="O27" s="152" t="n"/>
       <c r="P27" s="20" t="n"/>
